--- a/Cases.xlsx
+++ b/Cases.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="183">
   <si>
     <t>ID</t>
   </si>
@@ -855,17 +855,31 @@
   <si>
     <t>В ландшафтной ориентации не отображаются кнопки "Фильтровать" и "Отмена". Возможно на данной странице не работает скролл. Т.к. при переходе в книжный режим, кнопки появляются</t>
   </si>
+  <si>
+    <t>Автоматизация</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1282,192 +1296,129 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1476,110 +1427,176 @@
     <xf numFmtId="49" fontId="3" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1861,7 +1878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:J175"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5546875" style="10" bestFit="1" customWidth="1"/>
@@ -1873,10 +1890,11 @@
     <col min="7" max="7" width="60.44140625" style="15" customWidth="1"/>
     <col min="8" max="8" width="28.33203125" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.77734375" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="10"/>
+    <col min="10" max="10" width="21.21875" style="10" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1904,8 +1922,11 @@
       <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J1" s="100" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="73" t="s">
         <v>9</v>
       </c>
@@ -1928,7 +1949,7 @@
       <c r="H2" s="19"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="75" t="s">
         <v>10</v>
       </c>
@@ -1951,7 +1972,7 @@
       <c r="H3" s="29"/>
       <c r="I3" s="31"/>
     </row>
-    <row r="4" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="63" t="s">
         <v>44</v>
       </c>
@@ -1975,8 +1996,11 @@
         <v>24</v>
       </c>
       <c r="I4" s="46"/>
-    </row>
-    <row r="5" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="J4" s="100" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="65" t="s">
         <v>45</v>
       </c>
@@ -2003,7 +2027,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>46</v>
       </c>
@@ -2030,7 +2054,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="65" t="s">
         <v>47</v>
       </c>
@@ -2057,7 +2081,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>48</v>
       </c>
@@ -2082,7 +2106,7 @@
       </c>
       <c r="I8" s="52"/>
     </row>
-    <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="65" t="s">
         <v>49</v>
       </c>
@@ -2107,7 +2131,7 @@
       </c>
       <c r="I9" s="52"/>
     </row>
-    <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>50</v>
       </c>
@@ -2134,7 +2158,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="68" t="s">
         <v>60</v>
       </c>
@@ -2159,7 +2183,7 @@
       </c>
       <c r="I11" s="72"/>
     </row>
-    <row r="12" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>51</v>
       </c>
@@ -2184,7 +2208,7 @@
       </c>
       <c r="I12" s="21"/>
     </row>
-    <row r="13" spans="1:9" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="27" t="s">
         <v>56</v>
       </c>
@@ -2209,7 +2233,7 @@
       </c>
       <c r="I13" s="31"/>
     </row>
-    <row r="14" spans="1:9" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="42" t="s">
         <v>64</v>
       </c>
@@ -2232,7 +2256,7 @@
       <c r="H14" s="44"/>
       <c r="I14" s="46"/>
     </row>
-    <row r="15" spans="1:9" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="47" t="s">
         <v>69</v>
       </c>
@@ -2255,7 +2279,7 @@
       <c r="H15" s="51"/>
       <c r="I15" s="52"/>
     </row>
-    <row r="16" spans="1:9" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="47" t="s">
         <v>73</v>
       </c>
